--- a/reportes/reporte_ventas.xlsx
+++ b/reportes/reporte_ventas.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Ventas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,22 +438,22 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>producto</t>
+          <t>productos</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>cantidad</t>
+          <t>cantidad_total_productos</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>precio_unitario</t>
+          <t>total_vendido_pedido</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>subtotal</t>
+          <t>total_vendido_hasta_el_momento</t>
         </is>
       </c>
     </row>
@@ -463,7 +462,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46193.88647311285</v>
+        <v>46193.9749517657</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -472,101 +471,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pizza muzzarella</t>
+          <t>Pizza fugazzeta x1, Empanada de jamon y queso x3, Gaseosa x2, Empanada de jamon y queso x2</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>11200</v>
+        <v>23410.4</v>
       </c>
       <c r="G2" t="n">
-        <v>22400</v>
+        <v>23410.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46193.88647311285</v>
+        <v>46193.97576439361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Gaseosa</t>
+          <t>Pizza muzzarella x10</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>2500</v>
+        <v>114100</v>
       </c>
       <c r="G3" t="n">
-        <v>2500</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>producto</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>cantidad_vendida</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>total_recaudado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Pizza muzzarella</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>22400</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Gaseosa</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2500</v>
+        <v>137510.4</v>
       </c>
     </row>
   </sheetData>

--- a/reportes/reporte_ventas.xlsx
+++ b/reportes/reporte_ventas.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,98 +413,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>pedido_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>fecha</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>cliente</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>productos</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>cantidad_total_productos</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>total_vendido_pedido</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>total_vendido_hasta_el_momento</t>
+          <t>mensaje</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>46193.9749517657</v>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Todavía no existen ventas registradas.</t>
         </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Pizza fugazzeta x1, Empanada de jamon y queso x3, Gaseosa x2, Empanada de jamon y queso x2</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="n">
-        <v>23410.4</v>
-      </c>
-      <c r="G2" t="n">
-        <v>23410.4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>46193.97576439361</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Pizza muzzarella x10</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="n">
-        <v>114100</v>
-      </c>
-      <c r="G3" t="n">
-        <v>137510.4</v>
       </c>
     </row>
   </sheetData>

--- a/reportes/reporte_ventas.xlsx
+++ b/reportes/reporte_ventas.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,21 +417,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>mensaje</t>
+          <t>pedido_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>cliente</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>productos</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cantidad_total_productos</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>total_vendido_pedido</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>total_vendido_hasta_el_momento</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Todavía no existen ventas registradas.</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46194.0592336149</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Empanada de humita x1 ($1111.00), Pizza roquefort x3 ($42323.40)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43434.39999999999</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43434.39999999999</v>
       </c>
     </row>
   </sheetData>

--- a/reportes/reporte_ventas.xlsx
+++ b/reportes/reporte_ventas.xlsx
@@ -16,11 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +27,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00111827"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,9 +57,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -126,6 +142,22 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaVentas" displayName="TablaVentas" ref="A1:G2" headerRowCount="1">
+  <autoFilter ref="A1:G2"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Fecha"/>
+    <tableColumn id="3" name="Cliente"/>
+    <tableColumn id="4" name="Productos"/>
+    <tableColumn id="5" name="Cant. total"/>
+    <tableColumn id="6" name="Total pedido"/>
+    <tableColumn id="7" name="Total acumulado"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -419,72 +451,84 @@
   </sheetPr>
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>pedido_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>fecha</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>cliente</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>productos</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>cantidad_total_productos</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>total_vendido_pedido</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>total_vendido_hasta_el_momento</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Productos</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Cant. total</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total pedido</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Total acumulado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>46194.0592336149</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>yo</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Empanada de humita x1 ($1111.00), Pizza roquefort x3 ($42323.40)</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>43434.39999999999</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43434.39999999999</v>
+      <c r="B2" s="3" t="n">
+        <v>46195.99791228296</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Empanada de carne x5 ($4.000,00), Empanada de pollo x5 ($4.000,00), Gaseosa x5 ($8.500,00)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>16500</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>16500</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/reportes/reporte_ventas.xlsx
+++ b/reportes/reporte_ventas.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,12 +57,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -140,10 +145,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaVentas" displayName="TablaVentas" ref="A1:A2" headerRowCount="1">
-  <autoFilter ref="A1:A2"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="Estado"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaVentas" displayName="TablaVentas" ref="A1:K2" headerRowCount="1">
+  <autoFilter ref="A1:K2"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Fecha"/>
+    <tableColumn id="3" name="Cliente"/>
+    <tableColumn id="4" name="Entrega"/>
+    <tableColumn id="5" name="Dirección"/>
+    <tableColumn id="6" name="Productos"/>
+    <tableColumn id="7" name="Cant. total"/>
+    <tableColumn id="8" name="Subtotal"/>
+    <tableColumn id="9" name="Descuento"/>
+    <tableColumn id="10" name="Total pedido"/>
+    <tableColumn id="11" name="Total acumulado"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -438,24 +453,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Entrega</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Dirección</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Productos</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cant. total</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Total pedido</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Total acumulado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Todavia no existen ventas registradas.</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>46196.97478329071</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Bolivar 5852</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Empanada de humita x4 ($4.021,20) desc. $446,80, Empanada de jamón y queso x3 ($3.218,40) desc. $357,60, Pizza roquefort x4 ($56.739,20)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>64783.2</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>804.4000000000001</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>63978.8</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>63978.8</v>
       </c>
     </row>
   </sheetData>

--- a/reportes/reporte_ventas.xlsx
+++ b/reportes/reporte_ventas.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -57,15 +55,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -145,20 +140,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaVentas" displayName="TablaVentas" ref="A1:K2" headerRowCount="1">
-  <autoFilter ref="A1:K2"/>
-  <tableColumns count="11">
-    <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="Fecha"/>
-    <tableColumn id="3" name="Cliente"/>
-    <tableColumn id="4" name="Entrega"/>
-    <tableColumn id="5" name="Dirección"/>
-    <tableColumn id="6" name="Productos"/>
-    <tableColumn id="7" name="Cant. total"/>
-    <tableColumn id="8" name="Subtotal"/>
-    <tableColumn id="9" name="Descuento"/>
-    <tableColumn id="10" name="Total pedido"/>
-    <tableColumn id="11" name="Total acumulado"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaVentas" displayName="TablaVentas" ref="A1:A2" headerRowCount="1">
+  <autoFilter ref="A1:A2"/>
+  <tableColumns count="1">
+    <tableColumn id="1" name="Estado"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -453,120 +438,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Entrega</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Dirección</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Productos</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Cant. total</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Descuento</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Total pedido</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Total acumulado</t>
+          <t>Estado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>46196.97478329071</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Todavía no existen ventas registradas.</t>
         </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Bolivar 5852</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Empanada de humita x4 ($4.021,20) desc. $446,80, Empanada de jamón y queso x3 ($3.218,40) desc. $357,60, Pizza roquefort x4 ($56.739,20)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>64783.2</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>804.4000000000001</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>63978.8</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>63978.8</v>
       </c>
     </row>
   </sheetData>

--- a/reportes/reporte_ventas.xlsx
+++ b/reportes/reporte_ventas.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,12 +57,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -140,10 +145,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaVentas" displayName="TablaVentas" ref="A1:A2" headerRowCount="1">
-  <autoFilter ref="A1:A2"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="Estado"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaVentas" displayName="TablaVentas" ref="A1:K2" headerRowCount="1">
+  <autoFilter ref="A1:K2"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Fecha"/>
+    <tableColumn id="3" name="Cliente"/>
+    <tableColumn id="4" name="Entrega"/>
+    <tableColumn id="5" name="Dirección"/>
+    <tableColumn id="6" name="Productos"/>
+    <tableColumn id="7" name="Cant. total"/>
+    <tableColumn id="8" name="Subtotal"/>
+    <tableColumn id="9" name="Descuento"/>
+    <tableColumn id="10" name="Total pedido"/>
+    <tableColumn id="11" name="Total acumulado"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -438,24 +453,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Entrega</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Dirección</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Productos</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Cant. total</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Descuento</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Total pedido</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Total acumulado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Todavía no existen ventas registradas.</t>
-        </is>
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>46197.08334894492</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Empanada de verdura x6 ($5.696,70) desc. $1.005,30, Empanada de jamón y queso x6 ($6.079,20) desc. $1.072,80, Pizza napolitana x2 ($21.986,44) desc. $3.879,96, Gaseosa x2 ($4.306,10) desc. $759,90</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>44786.39999999999</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>6717.959999999999</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>38068.44</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>38068.44</v>
       </c>
     </row>
   </sheetData>

--- a/reportes/reporte_ventas.xlsx
+++ b/reportes/reporte_ventas.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -57,15 +55,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -145,20 +140,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaVentas" displayName="TablaVentas" ref="A1:K2" headerRowCount="1">
-  <autoFilter ref="A1:K2"/>
-  <tableColumns count="11">
-    <tableColumn id="1" name="ID"/>
-    <tableColumn id="2" name="Fecha"/>
-    <tableColumn id="3" name="Cliente"/>
-    <tableColumn id="4" name="Entrega"/>
-    <tableColumn id="5" name="Dirección"/>
-    <tableColumn id="6" name="Productos"/>
-    <tableColumn id="7" name="Cant. total"/>
-    <tableColumn id="8" name="Subtotal"/>
-    <tableColumn id="9" name="Descuento"/>
-    <tableColumn id="10" name="Total pedido"/>
-    <tableColumn id="11" name="Total acumulado"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaVentas" displayName="TablaVentas" ref="A1:A2" headerRowCount="1">
+  <autoFilter ref="A1:A2"/>
+  <tableColumns count="1">
+    <tableColumn id="1" name="Estado"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -453,116 +438,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Entrega</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Dirección</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Productos</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Cant. total</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Descuento</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Total pedido</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Total acumulado</t>
+          <t>Estado</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>46197.08334894492</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Todavía no existen ventas registradas.</t>
         </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Retiro</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Empanada de verdura x6 ($5.696,70) desc. $1.005,30, Empanada de jamón y queso x6 ($6.079,20) desc. $1.072,80, Pizza napolitana x2 ($21.986,44) desc. $3.879,96, Gaseosa x2 ($4.306,10) desc. $759,90</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>44786.39999999999</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>6717.959999999999</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>38068.44</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>38068.44</v>
       </c>
     </row>
   </sheetData>
